--- a/backend/exports/车队-港口映射导入模板.xlsx
+++ b/backend/exports/车队-港口映射导入模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aosom\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gihub\logix\backend\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2EFDF69-A8A7-40D4-9F47-AA134248E00F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AC9611-CA8A-42D9-9452-B1A9676C847A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -627,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="33.875" customWidth="1"/>
@@ -2080,11 +2080,17 @@
       </c>
     </row>
     <row r="61" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>15</v>
+      </c>
+      <c r="F61" t="s">
+        <v>39</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2101,10 +2107,10 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2124,7 +2130,7 @@
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -2147,7 +2153,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
@@ -2170,10 +2176,10 @@
         <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -2193,7 +2199,7 @@
         <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
         <v>39</v>
@@ -2216,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F67" t="s">
         <v>39</v>
@@ -2239,13 +2245,13 @@
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F68" t="s">
         <v>39</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -2265,7 +2271,7 @@
         <v>24</v>
       </c>
       <c r="F69" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G69">
         <v>5</v>
@@ -2285,13 +2291,13 @@
         <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F70" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -2305,19 +2311,22 @@
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="F71" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="G71">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H71">
         <v>0</v>
+      </c>
+      <c r="I71" t="s">
+        <v>64</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -2328,22 +2337,22 @@
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" t="s">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="F72" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I72" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -2360,7 +2369,7 @@
         <v>28</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G73">
         <v>10</v>
@@ -2383,16 +2392,16 @@
         <v>14</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F74" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G74">
         <v>10</v>
       </c>
       <c r="H74">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I74" t="s">
         <v>40</v>
@@ -2409,7 +2418,7 @@
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
@@ -2418,7 +2427,7 @@
         <v>10</v>
       </c>
       <c r="H75">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I75" t="s">
         <v>40</v>
@@ -2438,7 +2447,7 @@
         <v>29</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G76">
         <v>10</v>
@@ -2461,10 +2470,10 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G77">
         <v>10</v>
@@ -2487,7 +2496,7 @@
         <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
@@ -2505,32 +2514,6 @@
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.15">
-      <c r="B79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>29</v>
-      </c>
-      <c r="F79" t="s">
-        <v>23</v>
-      </c>
-      <c r="G79">
-        <v>10</v>
-      </c>
-      <c r="H79">
-        <v>50</v>
-      </c>
-      <c r="I79" t="s">
-        <v>40</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="M79" t="s">
         <v>31</v>
       </c>
     </row>
